--- a/series_data/secrets-anatolia/series_log.xlsx
+++ b/series_data/secrets-anatolia/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -814,6 +814,226 @@
       <c r="M7" t="inlineStr">
         <is>
           <t>C:\Users\ihsan\Desktop\Antigravity\Projects\Youtube\output\series\secrets-anatolia\episodes\ep01\shots\shot_06.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-06-17 18:00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/737c6ec5b860c129c27ad1524bfc88b9_1781719209.mp4</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/secrets-anatolia/episodes/ep02/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-06-17 18:02</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/0632522ece7dfc88866bcf23bfc72194_1781719357.mp4</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/secrets-anatolia/episodes/ep02/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-06-17 18:05</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b5f787fdc8cf7dcbbe49cb8828bcde65_1781719517.mp4</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/secrets-anatolia/episodes/ep02/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-17 18:07</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/7ff2575fe17150a8fcc8a5db17e8ca27_1781719647.mp4</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/secrets-anatolia/episodes/ep02/shots/shot_04.mp4</t>
         </is>
       </c>
     </row>

--- a/series_data/secrets-anatolia/series_log.xlsx
+++ b/series_data/secrets-anatolia/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1037,6 +1037,226 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-18 18:20</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/3beb03cbb189b9527d6eed20f269b9fd_1781806829.mp4</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/secrets-anatolia/episodes/ep03/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-06-18 18:22</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/6fe05c4d408aa9f0297f15984154eacd_1781806950.mp4</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/secrets-anatolia/episodes/ep03/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-18 18:25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/7cff686923d81bb127b987759cf8e192_1781807090.mp4</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/secrets-anatolia/episodes/ep03/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-18 18:28</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/f77c20f2732efe5d40fa7bd744fcb057_1781807294.mp4</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/secrets-anatolia/episodes/ep03/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/secrets-anatolia/series_log.xlsx
+++ b/series_data/secrets-anatolia/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1257,6 +1257,226 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-06-19 17:16</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ec7f5832f13e4f778ba6698bb4ec0052_1781889411.mp4</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/secrets-anatolia/episodes/ep04/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-06-19 17:19</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/8a4ac19cc76935f1ddaa37c808805d0e_1781889540.mp4</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/secrets-anatolia/episodes/ep04/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-19 17:22</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/32f0c26867e6c76a19546d0399ad2554_1781889726.mp4</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/secrets-anatolia/episodes/ep04/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-19 17:24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/5025af7b44f91507cd2831047a81b942_1781889844.mp4</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/secrets-anatolia/episodes/ep04/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/secrets-anatolia/series_log.xlsx
+++ b/series_data/secrets-anatolia/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1477,6 +1477,226 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-20 16:28</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/7d74b57136b8cfb51ff787d241712239_1781972926.mp4</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/secrets-anatolia/episodes/ep05/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-20 16:30</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/9d14a8c6eeb3596faa0d743665527cde_1781973023.mp4</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/secrets-anatolia/episodes/ep05/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-20 16:33</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/a0fc236a572a0d07aa3fd6284c4048a2_1781973179.mp4</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/secrets-anatolia/episodes/ep05/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-06-20 16:36</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ada24bc4f9926aad2b14f93c51687b81_1781973357.mp4</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/secrets-anatolia/episodes/ep05/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/secrets-anatolia/series_log.xlsx
+++ b/series_data/secrets-anatolia/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1697,6 +1697,226 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-06-22 18:07</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/86818ca363c25068726df5cc27854b64_1782151629.mp4</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/secrets-anatolia/episodes/ep06/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-06-22 18:09</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/4c4618f12114ef86ddec33545bacf84a_1782151756.mp4</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/secrets-anatolia/episodes/ep06/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-06-22 18:11</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/fe2ee06248d1de849d39d79d5aaab420_1782151892.mp4</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/secrets-anatolia/episodes/ep06/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-06-22 18:14</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/c94f2c50e4aecbc6e641d50d22976d4f_1782152057.mp4</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/secrets-anatolia/episodes/ep06/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/secrets-anatolia/series_log.xlsx
+++ b/series_data/secrets-anatolia/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1917,6 +1917,226 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-06-23 17:19</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/175cc50502f4de11df275356eedca104_1782235169.mp4</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/secrets-anatolia/episodes/ep07/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-06-23 17:22</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/13f26bedc85997fd83a4f5d06b87e29a_1782235347.mp4</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/secrets-anatolia/episodes/ep07/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-06-23 17:24</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/569966d2aba5c62bcaa8c1617c5db9f7_1782235477.mp4</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/secrets-anatolia/episodes/ep07/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-06-23 17:27</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/2b4c1c731a2fe6cff0692353c2e900e3_1782235599.mp4</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/secrets-anatolia/episodes/ep07/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/secrets-anatolia/series_log.xlsx
+++ b/series_data/secrets-anatolia/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2137,6 +2137,226 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-06-24 17:10</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/55c0439d514b8401a07134e7d882f7cb_1782321034.mp4</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/secrets-anatolia/episodes/ep08/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-06-24 17:13</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d1877d843eae51be0e92405b6b436021_1782321187.mp4</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/secrets-anatolia/episodes/ep08/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-06-24 17:16</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/055210015d5ae7ceb73e842cc91049c7_1782321404.mp4</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/secrets-anatolia/episodes/ep08/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-06-24 17:19</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/9677b6c765bbbfdb03a5c4662046ed13_1782321536.mp4</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/secrets-anatolia/episodes/ep08/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/secrets-anatolia/series_log.xlsx
+++ b/series_data/secrets-anatolia/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2357,6 +2357,226 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-06-25 17:19</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/71d3fca4c6330219e3d7276ebede3591_1782407951.mp4</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/secrets-anatolia/episodes/ep09/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-06-25 17:25</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/444c51e6e7e14e52dc3025c3b2278c3b_1782408323.mp4</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/secrets-anatolia/episodes/ep09/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-06-25 17:27</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/24f76dd3177888abd01c0b9f8566fe14_1782408460.mp4</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/secrets-anatolia/episodes/ep09/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-06-25 17:30</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d44723c8dffaa70eaa786a694c09ebe9_1782408639.mp4</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/secrets-anatolia/episodes/ep09/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/secrets-anatolia/series_log.xlsx
+++ b/series_data/secrets-anatolia/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2577,6 +2577,226 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-06-26 16:47</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/9c2bce00b543d741ad2c32770987b375_1782492466.mp4</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/secrets-anatolia/episodes/ep10/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-06-26 16:51</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/233437dc92a503d47560ef909fd1f4b2_1782492653.mp4</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/secrets-anatolia/episodes/ep10/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-06-26 16:54</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/539596090e0d79d516b0da507b590740_1782492839.mp4</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/secrets-anatolia/episodes/ep10/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-06-26 16:57</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/cb9b9ba5882d8e282b9a6f7251e9a6ec_1782493033.mp4</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/secrets-anatolia/episodes/ep10/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
